--- a/V_Model.xlsx
+++ b/V_Model.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Financials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAFDECCC-67C8-421F-8247-80658DBDFA31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A21C057-AD5E-4FC7-B706-9C186B18F057}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="809" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13290" yWindow="0" windowWidth="15615" windowHeight="15585" tabRatio="809" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -4811,10 +4811,10 @@
     <t>https://investor.visa.com/</t>
   </si>
   <si>
-    <t>10/31/2025</t>
-  </si>
-  <si>
     <t>Q3'25</t>
+  </si>
+  <si>
+    <t>1/10/2025</t>
   </si>
 </sst>
 </file>
@@ -11457,8 +11457,8 @@
       <sheetName val="Model"/>
       <sheetName val="Notes | Quant Analysis"/>
       <sheetName val="M&amp;A Scope"/>
+      <sheetName val="Markets | Product Lines"/>
       <sheetName val="Management"/>
-      <sheetName val="Markets | Product Lines"/>
       <sheetName val="Debt Schedule"/>
       <sheetName val="Clinical Trial Channel"/>
     </sheetNames>
@@ -12348,10 +12348,10 @@
         <v>1</v>
       </c>
       <c r="C3" s="72">
-        <v>341.29</v>
+        <v>350.28</v>
       </c>
       <c r="D3" s="43" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="F3"/>
     </row>
@@ -12364,7 +12364,7 @@
         <v>1830</v>
       </c>
       <c r="D4" s="45" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="5" spans="1:16">
@@ -12373,7 +12373,7 @@
       </c>
       <c r="C5" s="70">
         <f>C3*C4</f>
-        <v>624560.70000000007</v>
+        <v>641012.39999999991</v>
       </c>
     </row>
     <row r="6" spans="1:16">
@@ -12385,7 +12385,7 @@
         <v>16677</v>
       </c>
       <c r="D6" s="45" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="7" spans="1:16">
@@ -12397,7 +12397,7 @@
         <v>20762</v>
       </c>
       <c r="D7" s="45" t="s">
-        <v>1555</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="8" spans="1:16">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="C8" s="70">
         <f>C5-C6+C7</f>
-        <v>628645.70000000007</v>
+        <v>645097.39999999991</v>
       </c>
       <c r="D8" s="45"/>
     </row>
@@ -27159,7 +27159,7 @@
       </c>
       <c r="DE76" s="62">
         <f>Main!C3</f>
-        <v>341.29</v>
+        <v>350.28</v>
       </c>
     </row>
     <row r="77" spans="2:160" ht="15.75" customHeight="1">
@@ -27259,7 +27259,7 @@
       </c>
       <c r="DE77" s="61">
         <f>DE75/DE76-1</f>
-        <v>0.10464514922938362</v>
+        <v>7.6294230274341679E-2</v>
       </c>
       <c r="DF77" s="58" t="str">
         <f>IF(DE77&gt;0,"Upside","Downside")</f>
@@ -27393,7 +27393,7 @@
       <c r="DC78" s="35"/>
       <c r="DD78" s="73" t="str" cm="1">
         <f t="array" ref="DD78">_xlfn.IFS(DE77&gt;=25%,"Strong Buy",DE77&gt;=10.00001%,"Buy",AND(DE77&lt;=10%,DE77&gt;=-4.9999%),"Hold",AND(DE77&lt;=-5%,DE77&gt;=-14.999999%),"Sell",DE77&lt;=-15%,"Strong Sell")</f>
-        <v>Buy</v>
+        <v>Hold</v>
       </c>
       <c r="DE78" s="73"/>
       <c r="DF78" s="35"/>
